--- a/refs/heads/main/StructureDefinition-BundleRevisarLE.xlsx
+++ b/refs/heads/main/StructureDefinition-BundleRevisarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
